--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/o-higgins.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/o-higgins.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +15057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +15122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14901,7 +15837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14962,7 +15902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15023,7 +15967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15084,7 +16032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15145,7 +16097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15206,7 +16162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15267,7 +16227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15328,7 +16292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15389,7 +16357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15450,7 +16422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15511,7 +16487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15572,7 +16552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15633,7 +16617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15694,7 +16682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15755,7 +16747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15816,7 +16812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15877,7 +16877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15938,7 +16942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +17007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16060,7 +17072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16121,7 +17137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16182,7 +17202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16243,7 +17267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +17332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16365,7 +17397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16426,7 +17462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16487,7 +17527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16548,7 +17592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16609,7 +17657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16735,7 +17787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16796,7 +17852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16857,7 +17917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16918,7 +17982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16979,7 +18047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17040,7 +18112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17101,7 +18177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17162,7 +18242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17223,7 +18307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17284,7 +18372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17345,7 +18437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17406,7 +18502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17532,7 +18632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17593,7 +18697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17654,7 +18762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17715,7 +18827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17776,7 +18892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17837,7 +18957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17898,7 +19022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17959,7 +19087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18020,7 +19152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18081,7 +19217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18142,7 +19282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18203,7 +19347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18264,7 +19412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18325,7 +19477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18386,7 +19542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18447,7 +19607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18508,7 +19672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18569,7 +19737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18760,7 +19932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18821,7 +19997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18882,7 +20062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18943,7 +20127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19004,7 +20192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19065,7 +20257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19126,7 +20322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19187,7 +20387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19248,7 +20452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19309,7 +20517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19370,7 +20582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19431,7 +20647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19492,7 +20712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19553,7 +20777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19679,7 +20907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19740,7 +20972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19801,7 +21037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19862,7 +21102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19923,7 +21167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19984,7 +21232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20045,7 +21297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20106,7 +21362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20167,7 +21427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20228,7 +21492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20289,7 +21557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20350,7 +21622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20411,7 +21687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20472,7 +21752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20533,7 +21817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20594,7 +21882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20655,7 +21947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20716,7 +22012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20777,7 +22077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20838,7 +22142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20899,7 +22207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20960,7 +22272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21021,7 +22337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21082,7 +22402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21143,7 +22467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21269,7 +22597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21330,7 +22662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21391,7 +22727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21452,7 +22792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21513,7 +22857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21574,7 +22922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21635,7 +22987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21696,7 +23052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21757,7 +23117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21818,7 +23182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21879,7 +23247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21940,7 +23312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22001,7 +23377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22127,7 +23507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22188,7 +23572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22249,7 +23637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22310,7 +23702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22371,7 +23767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22432,7 +23832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22493,7 +23897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22554,7 +23962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22615,7 +24027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22676,7 +24092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22737,7 +24157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22798,7 +24222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22859,7 +24287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22920,7 +24352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22981,7 +24417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23042,7 +24482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23103,7 +24547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23164,7 +24612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23225,7 +24677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23286,7 +24742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23347,7 +24807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23408,7 +24872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23469,7 +24937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23595,7 +25067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23656,7 +25132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23717,7 +25197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23778,7 +25262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23839,7 +25327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23900,7 +25392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23961,7 +25457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24022,7 +25522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24083,7 +25587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24144,7 +25652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24205,7 +25717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24266,7 +25782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24327,7 +25847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24388,7 +25912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24514,7 +26042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24575,7 +26107,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24636,7 +26172,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24697,7 +26237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24758,7 +26302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24819,7 +26367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24880,7 +26432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24941,7 +26497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25002,7 +26562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25063,7 +26627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25124,7 +26692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25185,7 +26757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25246,7 +26822,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25307,7 +26887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25368,7 +26952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25429,7 +27017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25490,7 +27082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25551,7 +27147,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25612,7 +27212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25673,7 +27277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25734,7 +27342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25795,7 +27407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25856,7 +27472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25917,7 +27537,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25978,7 +27602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26039,7 +27667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26100,7 +27732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26161,7 +27797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26222,7 +27862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26283,7 +27927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26344,7 +27992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26405,7 +28057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26466,7 +28122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26527,7 +28187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26588,7 +28252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26649,7 +28317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26710,7 +28382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26771,7 +28447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26832,7 +28512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26893,7 +28577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26954,7 +28642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27015,7 +28707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27076,7 +28772,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27137,7 +28837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27198,7 +28902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27259,7 +28967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27320,7 +29032,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/o-higgins.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M440"/>
+  <dimension ref="A1:M442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10004,7 +10004,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>889473-1453-CM25</t>
+          <t>2080-30635-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10063,13 +10063,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>11378.34</v>
+        <v>12006.43</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2080-30635-CM25</t>
+          <t>889473-1453-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>12006.43</v>
+        <v>11378.34</v>
       </c>
     </row>
     <row r="150">
@@ -10199,7 +10199,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1620-229-CM25</t>
+          <t>1529-276-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10258,13 +10258,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>11338.91</v>
+        <v>46875.06</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1529-276-CM25</t>
+          <t>1620-229-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10323,7 +10323,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>46875.06</v>
+        <v>11338.91</v>
       </c>
     </row>
     <row r="153">
@@ -10459,7 +10459,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>522-129-CM25</t>
+          <t>1623-345-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.602.152-4</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hospital de Litueche</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10518,13 +10518,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>20740.86</v>
+        <v>11926.01</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1623-345-CM25</t>
+          <t>522-129-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.602.152-4</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>11926.01</v>
+        <v>20740.86</v>
       </c>
     </row>
     <row r="157">
@@ -10784,7 +10784,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>932-100-CM25</t>
+          <t>3374-115-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10843,13 +10843,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>210</v>
+        <v>2100.02</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>932-101-CM25</t>
+          <t>932-98-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10908,13 +10908,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>262.5</v>
+        <v>210</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>932-98-CM25</t>
+          <t>932-99-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3374-115-CM25</t>
+          <t>932-100-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11038,13 +11038,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2100.02</v>
+        <v>210</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>932-99-CM25</t>
+          <t>932-101-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>210</v>
+        <v>262.5</v>
       </c>
     </row>
     <row r="165">
@@ -11304,7 +11304,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1402-561-CM25</t>
+          <t>1402-562-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11363,13 +11363,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1766.21</v>
+        <v>11428.45</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1402-562-CM25</t>
+          <t>1402-561-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11428,13 +11428,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>11428.45</v>
+        <v>1766.21</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1623-389-CM25</t>
+          <t>1402-573-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11493,13 +11493,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>414.51</v>
+        <v>1036.26</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1623-388-CM25</t>
+          <t>1623-389-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11564,7 +11564,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1402-573-CM25</t>
+          <t>1623-388-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11589,12 +11589,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11623,13 +11623,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1036.26</v>
+        <v>414.51</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1529-322-CM25</t>
+          <t>1622-892-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11654,12 +11654,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11688,13 +11688,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>50935.62</v>
+        <v>23744.63</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1622-892-CM25</t>
+          <t>889473-1728-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11753,13 +11753,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>23744.63</v>
+        <v>11345.39</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>889473-1728-CM25</t>
+          <t>1529-322-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>11345.39</v>
+        <v>50935.62</v>
       </c>
     </row>
     <row r="176">
@@ -12149,7 +12149,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>897-45-CM25</t>
+          <t>897-46-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>4111.86</v>
+        <v>672.0599999999999</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>897-46-CM25</t>
+          <t>897-45-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>672.0599999999999</v>
+        <v>4111.86</v>
       </c>
     </row>
     <row r="183">
@@ -12409,7 +12409,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1623-439-CM25</t>
+          <t>2080-40984-CM25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12468,13 +12468,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>843.38</v>
+        <v>10542.19</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1398-2316-CM25</t>
+          <t>1623-439-CM25</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12499,12 +12499,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2266.91</v>
+        <v>843.38</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2080-40984-CM25</t>
+          <t>1398-2316-CM25</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>10542.19</v>
+        <v>2266.91</v>
       </c>
     </row>
     <row r="188">
@@ -12864,7 +12864,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2107-1642-CM25</t>
+          <t>1621-329-CM25</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12889,12 +12889,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12923,13 +12923,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>43913.76</v>
+        <v>7978.58</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1621-329-CM25</t>
+          <t>2107-1642-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12988,7 +12988,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>7978.58</v>
+        <v>43913.76</v>
       </c>
     </row>
     <row r="194">
@@ -13059,7 +13059,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2205-197-CM25</t>
+          <t>889473-1979-CM25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -13118,13 +13118,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>6115.64</v>
+        <v>10958.35</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>889473-1979-CM25</t>
+          <t>2205-197-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -13183,7 +13183,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>10958.35</v>
+        <v>6115.64</v>
       </c>
     </row>
     <row r="197">
@@ -14619,7 +14619,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1402-759-CM25</t>
+          <t>2080-42040-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14678,13 +14678,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1063.23</v>
+        <v>13928.32</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1623-522-CM25</t>
+          <t>2207-1194-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14704,17 +14704,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14743,13 +14743,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>9615.85</v>
+        <v>11418.83</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2207-1194-CM25</t>
+          <t>1402-759-CM25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14769,17 +14769,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14808,13 +14808,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>11418.83</v>
+        <v>1063.23</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2080-42040-CM25</t>
+          <t>1628-310-CM25</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14839,12 +14839,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14873,13 +14873,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>13928.32</v>
+        <v>12758.76</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1628-310-CM25</t>
+          <t>1623-522-CM25</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14938,13 +14938,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>12758.76</v>
+        <v>9615.85</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2107-1906-CM25</t>
+          <t>1626-220-CM25</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -15003,13 +15003,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>69831.66</v>
+        <v>6100.73</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1626-220-CM25</t>
+          <t>2107-1906-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15034,12 +15034,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -15068,13 +15068,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>6100.73</v>
+        <v>69831.66</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3374-148-CM25</t>
+          <t>3374-155-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>2115.06</v>
+        <v>41391.71</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>3374-155-CM25</t>
+          <t>2568-2197-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15164,12 +15164,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -15198,13 +15198,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>41391.71</v>
+        <v>4320.01</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2568-2197-CM25</t>
+          <t>3374-148-CM25</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -15263,7 +15263,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>4320.01</v>
+        <v>2115.06</v>
       </c>
     </row>
     <row r="229">
@@ -15724,7 +15724,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1620-286-CM25</t>
+          <t>1071580-34-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15744,17 +15744,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15783,13 +15783,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>10871.69</v>
+        <v>12115.26</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1624-291-CM25</t>
+          <t>1620-286-CM25</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15814,12 +15814,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15848,13 +15848,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>8953.59</v>
+        <v>10871.69</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1071580-34-CM25</t>
+          <t>1624-291-CM25</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15874,17 +15874,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15913,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>12115.26</v>
+        <v>8953.59</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1622-1133-CM25</t>
+          <t>1398-2657-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15944,12 +15944,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15978,13 +15978,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>22604.95</v>
+        <v>3552.53</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1398-2657-CM25</t>
+          <t>1622-1133-CM25</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -16009,12 +16009,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -16043,7 +16043,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>3552.53</v>
+        <v>22604.95</v>
       </c>
     </row>
     <row r="241">
@@ -16504,7 +16504,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1623-572-CM25</t>
+          <t>905-299-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16529,12 +16529,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16563,13 +16563,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>217.52</v>
+        <v>1370.37</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1623-573-CM25</t>
+          <t>1623-572-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16628,13 +16628,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>12507.34</v>
+        <v>217.52</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>905-299-CM25</t>
+          <t>1623-573-CM25</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16659,12 +16659,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16693,13 +16693,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1370.37</v>
+        <v>12507.34</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2568-2265-CM25</t>
+          <t>1350767-123-CM25</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16724,12 +16724,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.981.210-7</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2230.39</v>
+        <v>60976.94</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1350767-123-CM25</t>
+          <t>1628-368-CM25</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16789,12 +16789,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.981.210-7</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16823,13 +16823,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>60976.94</v>
+        <v>16303.99</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1628-368-CM25</t>
+          <t>2568-2265-CM25</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16854,12 +16854,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>16303.99</v>
+        <v>2230.39</v>
       </c>
     </row>
     <row r="254">
@@ -17219,7 +17219,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2080-56569-CM25</t>
+          <t>615-100-CM25</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.802.006-1</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -17278,13 +17278,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>11522.15</v>
+        <v>770.12</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1620-305-CM25</t>
+          <t>2080-56569-CM25</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17309,12 +17309,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -17343,13 +17343,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>14170.53</v>
+        <v>11522.15</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>615-100-CM25</t>
+          <t>1620-305-CM25</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17374,12 +17374,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.802.006-1</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17408,7 +17408,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>770.12</v>
+        <v>14170.53</v>
       </c>
     </row>
     <row r="262">
@@ -18584,7 +18584,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1402-15-CM26</t>
+          <t>1402-14-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18643,13 +18643,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1252.55</v>
+        <v>3643.78</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1402-14-CM26</t>
+          <t>1402-15-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18708,13 +18708,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>3643.78</v>
+        <v>1252.55</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1402-13-CM26</t>
+          <t>2205-7-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18739,12 +18739,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18773,13 +18773,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>11465</v>
+        <v>6739.81</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2107-170-CM26</t>
+          <t>1402-13-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18804,12 +18804,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18838,13 +18838,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>36687.99</v>
+        <v>11465</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2205-7-CM26</t>
+          <t>2107-170-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18869,12 +18869,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>6739.81</v>
+        <v>36687.99</v>
       </c>
     </row>
     <row r="285">
@@ -20209,7 +20209,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2207-174-CM26</t>
+          <t>1529-58-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20229,17 +20229,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20268,13 +20268,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>13182.44</v>
+        <v>52806.6</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1529-58-CM26</t>
+          <t>2207-174-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20294,17 +20294,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>52806.6</v>
+        <v>13182.44</v>
       </c>
     </row>
     <row r="307">
@@ -20794,12 +20794,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1627-369-SE26</t>
+          <t>2205-40-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -20819,12 +20819,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -20853,18 +20853,18 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>79005.72</v>
+        <v>6423.65</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2205-40-CM26</t>
+          <t>1627-369-SE26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -20884,12 +20884,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20918,7 +20918,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>6423.65</v>
+        <v>79005.72</v>
       </c>
     </row>
     <row r="316">
@@ -21119,7 +21119,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>1193180-16-CM26</t>
+          <t>2188-82-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -21144,12 +21144,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>60.511.060-6</t>
+          <t>61.602.134-6</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL LIBERTADOR BERNARDO  O´HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -21178,13 +21178,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1029.41</v>
+        <v>38992.69</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1529-88-CM26</t>
+          <t>1193180-16-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -21209,12 +21209,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>60.511.060-6</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL LIBERTADOR BERNARDO  O´HIGGINS</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -21243,13 +21243,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>49453.98</v>
+        <v>1029.41</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2188-82-CM26</t>
+          <t>1529-88-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -21274,12 +21274,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>61.602.134-6</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -21308,7 +21308,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>38992.69</v>
+        <v>49453.98</v>
       </c>
     </row>
     <row r="322">
@@ -21769,7 +21769,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>5336-9-CM26</t>
+          <t>1621-109-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21794,12 +21794,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>65.705.920-k</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21828,13 +21828,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1062.44</v>
+        <v>11702.37</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2568-91-CM26</t>
+          <t>5336-9-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21859,12 +21859,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.705.920-k</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21893,13 +21893,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2974.83</v>
+        <v>1062.44</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1621-109-CM26</t>
+          <t>2568-91-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21924,12 +21924,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21958,7 +21958,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>11702.37</v>
+        <v>2974.83</v>
       </c>
     </row>
     <row r="332">
@@ -22354,12 +22354,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1529-132-CM26</t>
+          <t>1627-549-SE26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -22379,12 +22379,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22413,7 +22413,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>51398.12</v>
+        <v>76349.73</v>
       </c>
     </row>
     <row r="339">
@@ -22484,12 +22484,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1627-549-SE26</t>
+          <t>1529-132-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -22509,12 +22509,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -22543,7 +22543,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>76349.73</v>
+        <v>51398.12</v>
       </c>
     </row>
     <row r="341">
@@ -22939,7 +22939,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1623-201-CM26</t>
+          <t>2207-378-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22959,17 +22959,17 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22998,13 +22998,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>335.48</v>
+        <v>12641.88</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2207-378-CM26</t>
+          <t>1623-201-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -23024,17 +23024,17 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>12641.88</v>
+        <v>335.48</v>
       </c>
     </row>
     <row r="349">
@@ -23134,7 +23134,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1621-147-CM26</t>
+          <t>2205-76-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -23159,12 +23159,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -23193,13 +23193,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>11606.06</v>
+        <v>6520.26</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2205-76-CM26</t>
+          <t>1621-147-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23224,12 +23224,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -23258,7 +23258,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>6520.26</v>
+        <v>11606.06</v>
       </c>
     </row>
     <row r="352">
@@ -23784,7 +23784,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2107-1024-CM26</t>
+          <t>1626-110-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23809,12 +23809,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23843,13 +23843,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>47037.22</v>
+        <v>6248.43</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1626-110-CM26</t>
+          <t>2107-1024-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23874,12 +23874,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23908,7 +23908,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>6248.43</v>
+        <v>47037.22</v>
       </c>
     </row>
     <row r="362">
@@ -24174,7 +24174,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2205-86-CM26</t>
+          <t>3374-73-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24199,12 +24199,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24233,13 +24233,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>6414.95</v>
+        <v>3273.71</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>3374-76-CM26</t>
+          <t>2205-86-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24264,12 +24264,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -24298,13 +24298,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>6547.43</v>
+        <v>6414.95</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>3374-73-CM26</t>
+          <t>3374-76-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>3273.71</v>
+        <v>6547.43</v>
       </c>
     </row>
     <row r="369">
@@ -24759,7 +24759,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>889473-1013-CM26</t>
+          <t>1628-208-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24784,12 +24784,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -24818,13 +24818,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>11231.36</v>
+        <v>16279.22</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1628-208-CM26</t>
+          <t>889473-1013-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -24849,12 +24849,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -24883,18 +24883,18 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>16279.22</v>
+        <v>11231.36</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1622-838-CM26</t>
+          <t>1627-886-SE26</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -24914,12 +24914,12 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -24948,18 +24948,18 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>23992.06</v>
+        <v>80771.59</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1627-886-SE26</t>
+          <t>1622-838-CM26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -24979,12 +24979,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -25013,7 +25013,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>80771.59</v>
+        <v>23992.06</v>
       </c>
     </row>
     <row r="379">
@@ -25214,7 +25214,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1626-130-CM26</t>
+          <t>522-130-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -25239,12 +25239,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.152-4</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -25273,13 +25273,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>6357.98</v>
+        <v>17252.49</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>522-130-CM26</t>
+          <t>1626-130-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25304,12 +25304,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>61.602.152-4</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Hospital de Litueche</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -25338,7 +25338,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>17252.49</v>
+        <v>6357.98</v>
       </c>
     </row>
     <row r="384">
@@ -26124,7 +26124,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1079563-312-CM26</t>
+          <t>1622-998-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -26149,12 +26149,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -26164,12 +26164,12 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -26183,13 +26183,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>213.77</v>
+        <v>23515.08</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>889473-1275-CM26</t>
+          <t>1079563-312-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -26214,12 +26214,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -26229,12 +26229,12 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -26248,13 +26248,13 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>11011.21</v>
+        <v>213.77</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1622-998-CM26</t>
+          <t>889473-1275-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26279,12 +26279,12 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>23515.08</v>
+        <v>11011.21</v>
       </c>
     </row>
     <row r="399">
@@ -26969,12 +26969,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1622-1104-CM26</t>
+          <t>1627-1161-SE26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -26989,17 +26989,17 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -27028,13 +27028,13 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>25146.51</v>
+        <v>84659.45</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>889473-1465-CM26</t>
+          <t>1622-1104-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -27059,12 +27059,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -27093,13 +27093,13 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>11263.19</v>
+        <v>25146.51</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2107-1711-CM26</t>
+          <t>889473-1465-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -27124,12 +27124,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -27139,12 +27139,12 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
@@ -27158,13 +27158,13 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>56852.97</v>
+        <v>11263.19</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2080-8552-CM26</t>
+          <t>2107-1711-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -27179,7 +27179,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -27189,12 +27189,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -27204,12 +27204,12 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -27223,13 +27223,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>12617.69</v>
+        <v>56852.97</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2205-123-CM26</t>
+          <t>1624-196-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27254,12 +27254,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -27288,7 +27288,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>6397.64</v>
+        <v>9916.34</v>
       </c>
     </row>
     <row r="414">
@@ -27359,7 +27359,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1624-196-CM26</t>
+          <t>2080-8552-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27384,12 +27384,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -27418,13 +27418,13 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>9916.34</v>
+        <v>12617.69</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>1620-202-CM26</t>
+          <t>2205-123-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -27439,7 +27439,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -27449,12 +27449,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -27483,13 +27483,13 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>17421.51</v>
+        <v>6397.64</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1529-230-CM26</t>
+          <t>1620-202-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -27514,12 +27514,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -27529,12 +27529,12 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
@@ -27548,13 +27548,13 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>51773.38</v>
+        <v>17421.51</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>594965-148-CM26</t>
+          <t>1529-230-CM26</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -27564,12 +27564,12 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -27579,12 +27579,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
@@ -27613,13 +27613,13 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>531.5599999999999</v>
+        <v>51773.38</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>1626-181-CM26</t>
+          <t>615-57-CM26</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -27644,12 +27644,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.802.006-1</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -27678,13 +27678,13 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>6399.94</v>
+        <v>3086.47</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>615-57-CM26</t>
+          <t>522-176-CM26</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27709,12 +27709,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>61.802.006-1</t>
+          <t>61.602.152-4</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -27743,13 +27743,13 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>3086.47</v>
+        <v>19213.18</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>522-176-CM26</t>
+          <t>594965-148-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27774,12 +27774,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>61.602.152-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Hospital de Litueche</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -27808,13 +27808,13 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>19213.18</v>
+        <v>531.5599999999999</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2207-700-CM26</t>
+          <t>1626-181-CM26</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -27829,22 +27829,22 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -27873,13 +27873,13 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>18682.72</v>
+        <v>6399.94</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>1621-256-CM26</t>
+          <t>2207-700-CM26</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -27894,22 +27894,22 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -27938,7 +27938,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>11559.34</v>
+        <v>18682.72</v>
       </c>
     </row>
     <row r="424">
@@ -28009,7 +28009,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>804962-144-CM26</t>
+          <t>1621-256-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -28024,22 +28024,22 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>69.081.400-5</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLIVAR</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -28068,13 +28068,13 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>1818.46</v>
+        <v>11559.34</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>1624-207-CM26</t>
+          <t>804962-144-CM26</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -28089,22 +28089,22 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>69.081.400-5</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>I MUNICIPALIDAD DE OLIVAR</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -28133,13 +28133,13 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>9643.98</v>
+        <v>1818.46</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>3374-122-CM26</t>
+          <t>1624-207-CM26</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -28164,12 +28164,12 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -28198,13 +28198,13 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>2088.71</v>
+        <v>9643.98</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2188-298-CM26</t>
+          <t>3374-122-CM26</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -28219,7 +28219,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -28229,12 +28229,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>61.602.134-6</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -28263,13 +28263,13 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>33494.88</v>
+        <v>2088.71</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>889473-1659-CM26</t>
+          <t>2188-298-CM26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -28284,22 +28284,22 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.134-6</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -28328,13 +28328,13 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>1048.08</v>
+        <v>33494.88</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2205-152-CM26</t>
+          <t>889473-1659-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -28349,22 +28349,22 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -28393,13 +28393,13 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>7350</v>
+        <v>1048.08</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>594965-158-CM26</t>
+          <t>2205-152-CM26</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -28414,22 +28414,22 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -28458,13 +28458,13 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>48270.48</v>
+        <v>7350</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>1620-216-CM26</t>
+          <t>594965-158-CM26</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -28479,22 +28479,22 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -28523,13 +28523,13 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>16677.54</v>
+        <v>48270.48</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>1622-1234-CM26</t>
+          <t>1620-216-CM26</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -28544,7 +28544,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -28554,12 +28554,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -28588,13 +28588,13 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>24852.18</v>
+        <v>16677.54</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>3374-126-CM26</t>
+          <t>1622-1234-CM26</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -28619,12 +28619,12 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -28653,13 +28653,13 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>184.49</v>
+        <v>24852.18</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2080-9855-CM26</t>
+          <t>3374-126-CM26</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -28679,17 +28679,17 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -28718,13 +28718,13 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>11924.84</v>
+        <v>184.49</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2107-2009-CM26</t>
+          <t>2080-9855-CM26</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -28749,12 +28749,12 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -28764,12 +28764,12 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -28783,13 +28783,13 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>53936.31</v>
+        <v>11924.84</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2207-772-CM26</t>
+          <t>2107-2009-CM26</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -28804,22 +28804,22 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -28829,12 +28829,12 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
@@ -28848,13 +28848,13 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>14431.68</v>
+        <v>53936.31</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>889473-1764-CM26</t>
+          <t>1628-294-CM26</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -28879,12 +28879,12 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -28913,13 +28913,13 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>7130.95</v>
+        <v>15468.7</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>1628-294-CM26</t>
+          <t>2207-772-CM26</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -28939,17 +28939,17 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -28978,72 +28978,202 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>15468.7</v>
+        <v>14431.68</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
+          <t>889473-1764-CM26</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>61.980.530-5</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M440" s="2" t="n">
+        <v>7130.95</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
           <t>1529-249-CM26</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr">
+      <c r="B441" t="inlineStr">
         <is>
           <t>2239-1-LR26</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr">
+      <c r="C441" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr">
+      <c r="D441" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E440" t="inlineStr">
+      <c r="E441" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F440" t="inlineStr">
+      <c r="F441" t="inlineStr">
         <is>
           <t>61.602.140-0</t>
         </is>
       </c>
-      <c r="G440" t="inlineStr">
+      <c r="G441" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
-      <c r="H440" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="I440" t="inlineStr">
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
         <is>
           <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
-      <c r="J440" t="inlineStr">
+      <c r="J441" t="inlineStr">
         <is>
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L440" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M440" s="2" t="n">
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M441" s="2" t="n">
         <v>50076.5</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>1627-1299-SE26</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>2239-2-LR21</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>61.602.145-1</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M442" s="2" t="n">
+        <v>82847.95</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/o-higgins.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M442"/>
+  <dimension ref="A1:M451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1164,7 +1164,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1402-59-CM25</t>
+          <t>3374-1-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2903.02</v>
+        <v>2015.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1622-131-CM25</t>
+          <t>2080-5931-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>24191.84</v>
+        <v>2015.99</v>
       </c>
     </row>
     <row r="14">
@@ -1359,7 +1359,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2080-5931-CM25</t>
+          <t>1622-131-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2015.99</v>
+        <v>24191.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3374-1-CM25</t>
+          <t>1402-59-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2015.99</v>
+        <v>2903.02</v>
       </c>
     </row>
     <row r="17">
@@ -2139,7 +2139,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1402-66-CM25</t>
+          <t>2207-64-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2159,17 +2159,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2970.69</v>
+        <v>9799.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2207-64-CM25</t>
+          <t>1402-66-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2224,17 +2224,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>9799.17</v>
+        <v>2970.69</v>
       </c>
     </row>
     <row r="29">
@@ -3179,7 +3179,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>626788-14-CM25</t>
+          <t>2205-36-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.980.040-0</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>403.99</v>
+        <v>6838.04</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2205-36-CM25</t>
+          <t>2207-246-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3264,17 +3264,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>6838.04</v>
+        <v>11569.89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2207-246-CM25</t>
+          <t>626788-14-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3329,17 +3329,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.980.040-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>11569.89</v>
+        <v>403.99</v>
       </c>
     </row>
     <row r="46">
@@ -3829,7 +3829,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1402-167-CM25</t>
+          <t>1339542-20-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3849,17 +3849,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3888,13 +3888,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>4416.91</v>
+        <v>2686.59</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2080-23630-CM25</t>
+          <t>1402-166-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>11957.56</v>
+        <v>6453.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1402-166-CM25</t>
+          <t>1402-167-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>6453.6</v>
+        <v>4416.91</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1339542-20-CM25</t>
+          <t>2080-23630-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2686.59</v>
+        <v>11957.56</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1529-119-CM25</t>
+          <t>1402-170-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>44964.82</v>
+        <v>6976.52</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1620-92-CM25</t>
+          <t>1529-119-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7522.51</v>
+        <v>44964.82</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1402-170-CM25</t>
+          <t>1620-92-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>6976.52</v>
+        <v>7522.51</v>
       </c>
     </row>
     <row r="60">
@@ -4479,7 +4479,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1623-132-CM25</t>
+          <t>2207-315-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4499,17 +4499,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>12176.13</v>
+        <v>11307.02</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2107-521-CM25</t>
+          <t>2081-27-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>60.511.062-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE COLCHAGUA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>36848.7</v>
+        <v>631.6900000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4674,7 +4674,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2207-315-CM25</t>
+          <t>2107-521-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4694,17 +4694,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>11307.02</v>
+        <v>36848.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2081-27-CM25</t>
+          <t>1623-132-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.511.062-2</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE COLCHAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>631.6900000000001</v>
+        <v>12176.13</v>
       </c>
     </row>
     <row r="68">
@@ -5519,7 +5519,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>889473-619-CM25</t>
+          <t>594965-40-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8803.620000000001</v>
+        <v>7835.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>594965-40-CM25</t>
+          <t>889473-619-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>7835.6</v>
+        <v>8803.620000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5714,7 +5714,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1193180-29-CM25</t>
+          <t>1211-27-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>60.511.060-6</t>
+          <t>60.901.008-8</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL LIBERTADOR BERNARDO  O´HIGGINS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1350.93</v>
+        <v>426.39</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1211-27-CM25</t>
+          <t>1193180-29-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.901.008-8</t>
+          <t>60.511.060-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL LIBERTADOR BERNARDO  O´HIGGINS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>426.39</v>
+        <v>1350.93</v>
       </c>
     </row>
     <row r="84">
@@ -6039,7 +6039,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1529-168-CM25</t>
+          <t>2107-703-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6098,13 +6098,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>47468.55</v>
+        <v>45482.43</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2107-703-CM25</t>
+          <t>1529-168-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>45482.43</v>
+        <v>47468.55</v>
       </c>
     </row>
     <row r="89">
@@ -6494,7 +6494,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5336-13-CM25</t>
+          <t>1626-70-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6519,12 +6519,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>65.705.920-k</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6553,13 +6553,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2117.31</v>
+        <v>6305.9</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1626-70-CM25</t>
+          <t>5336-13-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>65.705.920-k</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>6305.9</v>
+        <v>2117.31</v>
       </c>
     </row>
     <row r="96">
@@ -6689,7 +6689,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>594965-60-CM25</t>
+          <t>1622-580-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6748,13 +6748,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1001.44</v>
+        <v>22225.99</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1622-580-CM25</t>
+          <t>2205-107-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>22225.99</v>
+        <v>6221.79</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2205-107-CM25</t>
+          <t>594965-60-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>6221.79</v>
+        <v>1001.44</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1402-326-CM25</t>
+          <t>2080-28838-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>10629.14</v>
+        <v>9566.219999999999</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2080-28838-CM25</t>
+          <t>1402-326-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>9566.219999999999</v>
+        <v>10629.14</v>
       </c>
     </row>
     <row r="102">
@@ -7339,7 +7339,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1628-121-CM25</t>
+          <t>1398-1824-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7398,13 +7398,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>13875.7</v>
+        <v>3750.76</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1624-120-CM25</t>
+          <t>1628-121-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7463,13 +7463,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>8790.459999999999</v>
+        <v>13875.7</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1398-1824-CM25</t>
+          <t>1624-120-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3750.76</v>
+        <v>8790.459999999999</v>
       </c>
     </row>
     <row r="110">
@@ -7599,7 +7599,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1350767-54-CM25</t>
+          <t>2087-34-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.981.210-7</t>
+          <t>60.511.141-6</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CARDENAL CARO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7658,13 +7658,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>30950.57</v>
+        <v>375.63</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2087-34-CM25</t>
+          <t>2087-35-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>375.63</v>
+        <v>281.72</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2087-35-CM25</t>
+          <t>1350767-54-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>60.511.141-6</t>
+          <t>61.981.210-7</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CARDENAL CARO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>281.72</v>
+        <v>30950.57</v>
       </c>
     </row>
     <row r="114">
@@ -7859,7 +7859,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>889473-1118-CM25</t>
+          <t>2207-638-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2718.03</v>
+        <v>11469.68</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2207-638-CM25</t>
+          <t>3374-87-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7983,13 +7983,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>11469.68</v>
+        <v>23495.24</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3374-87-CM25</t>
+          <t>889473-1118-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>23495.24</v>
+        <v>2718.03</v>
       </c>
     </row>
     <row r="118">
@@ -8184,7 +8184,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2080-29771-CM25</t>
+          <t>1402-422-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8243,13 +8243,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>8419.629999999999</v>
+        <v>10524.54</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1402-422-CM25</t>
+          <t>2080-29771-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>10524.54</v>
+        <v>8419.629999999999</v>
       </c>
     </row>
     <row r="122">
@@ -8704,7 +8704,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1622-692-CM25</t>
+          <t>1402-449-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8763,13 +8763,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>21373.46</v>
+        <v>1068.67</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1402-449-CM25</t>
+          <t>1622-692-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1068.67</v>
+        <v>21373.46</v>
       </c>
     </row>
     <row r="130">
@@ -9289,7 +9289,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1628-164-CM25</t>
+          <t>3374-98-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9348,13 +9348,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>13943.41</v>
+        <v>4290.28</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3374-98-CM25</t>
+          <t>1628-164-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4290.28</v>
+        <v>13943.41</v>
       </c>
     </row>
     <row r="139">
@@ -9744,7 +9744,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1071580-22-CM25</t>
+          <t>1621-268-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9764,17 +9764,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>10041.19</v>
+        <v>8021.78</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1621-268-CM25</t>
+          <t>1622-791-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9868,13 +9868,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>8021.78</v>
+        <v>21024.53</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1402-490-CM25</t>
+          <t>1071580-22-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9894,17 +9894,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9933,13 +9933,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>10512.26</v>
+        <v>10041.19</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1622-791-CM25</t>
+          <t>1402-490-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>21024.53</v>
+        <v>10512.26</v>
       </c>
     </row>
     <row r="148">
@@ -10329,7 +10329,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2107-1218-CM25</t>
+          <t>1624-172-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10388,13 +10388,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>40950.04</v>
+        <v>8425.51</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1624-172-CM25</t>
+          <t>2107-1218-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>8425.51</v>
+        <v>40950.04</v>
       </c>
     </row>
     <row r="155">
@@ -10784,7 +10784,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3374-115-CM25</t>
+          <t>932-98-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10843,13 +10843,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2100.02</v>
+        <v>210</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>932-98-CM25</t>
+          <t>932-99-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10914,7 +10914,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>932-99-CM25</t>
+          <t>932-100-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>932-100-CM25</t>
+          <t>932-101-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11038,13 +11038,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>210</v>
+        <v>262.5</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>932-101-CM25</t>
+          <t>3374-115-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11069,12 +11069,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>262.5</v>
+        <v>2100.02</v>
       </c>
     </row>
     <row r="165">
@@ -11304,7 +11304,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1402-562-CM25</t>
+          <t>1402-561-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11363,13 +11363,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>11428.45</v>
+        <v>1766.21</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1402-561-CM25</t>
+          <t>1402-562-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11428,13 +11428,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1766.21</v>
+        <v>11428.45</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1402-573-CM25</t>
+          <t>1623-388-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11493,7 +11493,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1036.26</v>
+        <v>414.51</v>
       </c>
     </row>
     <row r="171">
@@ -11564,7 +11564,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1623-388-CM25</t>
+          <t>1402-573-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11589,12 +11589,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11623,13 +11623,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>414.51</v>
+        <v>1036.26</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1622-892-CM25</t>
+          <t>889473-1728-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11654,12 +11654,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11688,13 +11688,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>23744.63</v>
+        <v>11345.39</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>889473-1728-CM25</t>
+          <t>1529-322-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11753,13 +11753,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>11345.39</v>
+        <v>50935.62</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1529-322-CM25</t>
+          <t>1622-892-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>50935.62</v>
+        <v>23744.63</v>
       </c>
     </row>
     <row r="176">
@@ -12149,7 +12149,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>897-46-CM25</t>
+          <t>897-45-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>672.0599999999999</v>
+        <v>4111.86</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>897-45-CM25</t>
+          <t>897-46-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>4111.86</v>
+        <v>672.0599999999999</v>
       </c>
     </row>
     <row r="183">
@@ -12864,7 +12864,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1621-329-CM25</t>
+          <t>2107-1642-CM25</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12889,12 +12889,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12923,13 +12923,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>7978.58</v>
+        <v>43913.76</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2107-1642-CM25</t>
+          <t>1621-329-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12988,7 +12988,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>43913.76</v>
+        <v>7978.58</v>
       </c>
     </row>
     <row r="194">
@@ -13059,7 +13059,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>889473-1979-CM25</t>
+          <t>2205-197-CM25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -13118,13 +13118,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>10958.35</v>
+        <v>6115.64</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2205-197-CM25</t>
+          <t>889473-1979-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -13183,7 +13183,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>6115.64</v>
+        <v>10958.35</v>
       </c>
     </row>
     <row r="197">
@@ -13579,7 +13579,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1623-468-CM25</t>
+          <t>2205-206-CM25</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13599,17 +13599,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13638,13 +13638,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>311.98</v>
+        <v>6113.29</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1623-469-CM25</t>
+          <t>1623-468-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13709,7 +13709,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2205-206-CM25</t>
+          <t>697057-116-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13729,17 +13729,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13768,13 +13768,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>6113.29</v>
+        <v>2123.11</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>697057-116-CM25</t>
+          <t>1623-469-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13799,12 +13799,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13833,7 +13833,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2123.11</v>
+        <v>311.98</v>
       </c>
     </row>
     <row r="207">
@@ -14229,7 +14229,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1621-356-CM25</t>
+          <t>1620-277-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14254,12 +14254,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14288,13 +14288,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>8103.9</v>
+        <v>15929.27</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1626-203-CM25</t>
+          <t>2107-1889-CM25</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14319,12 +14319,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -14353,13 +14353,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2113.02</v>
+        <v>73277.19</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1620-277-CM25</t>
+          <t>1621-356-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14384,12 +14384,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14418,13 +14418,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>15929.27</v>
+        <v>8103.9</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2107-1889-CM25</t>
+          <t>1626-203-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14449,12 +14449,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14483,7 +14483,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>73277.19</v>
+        <v>2113.02</v>
       </c>
     </row>
     <row r="217">
@@ -14619,7 +14619,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2080-42040-CM25</t>
+          <t>1623-522-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14678,13 +14678,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>13928.32</v>
+        <v>9615.85</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2207-1194-CM25</t>
+          <t>2080-42040-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14704,17 +14704,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14743,13 +14743,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>11418.83</v>
+        <v>13928.32</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1402-759-CM25</t>
+          <t>2207-1194-CM25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14769,17 +14769,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14808,13 +14808,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1063.23</v>
+        <v>11418.83</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1628-310-CM25</t>
+          <t>1402-759-CM25</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14839,12 +14839,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14873,13 +14873,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>12758.76</v>
+        <v>1063.23</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1623-522-CM25</t>
+          <t>1628-310-CM25</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14938,13 +14938,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>9615.85</v>
+        <v>12758.76</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1626-220-CM25</t>
+          <t>2107-1906-CM25</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -15003,13 +15003,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>6100.73</v>
+        <v>69831.66</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2107-1906-CM25</t>
+          <t>1626-220-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15034,12 +15034,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -15068,13 +15068,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>69831.66</v>
+        <v>6100.73</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3374-155-CM25</t>
+          <t>3374-148-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>41391.71</v>
+        <v>2115.06</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2568-2197-CM25</t>
+          <t>3374-155-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15164,12 +15164,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -15198,13 +15198,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>4320.01</v>
+        <v>41391.71</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3374-148-CM25</t>
+          <t>2568-2197-CM25</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -15263,7 +15263,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2115.06</v>
+        <v>4320.01</v>
       </c>
     </row>
     <row r="229">
@@ -15724,7 +15724,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1071580-34-CM25</t>
+          <t>1624-291-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15744,17 +15744,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15783,7 +15783,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>12115.26</v>
+        <v>8953.59</v>
       </c>
     </row>
     <row r="237">
@@ -15854,7 +15854,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1624-291-CM25</t>
+          <t>1071580-34-CM25</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15874,17 +15874,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15913,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>8953.59</v>
+        <v>12115.26</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1398-2657-CM25</t>
+          <t>1622-1133-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15944,12 +15944,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15978,13 +15978,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3552.53</v>
+        <v>22604.95</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1622-1133-CM25</t>
+          <t>1398-2657-CM25</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -16009,12 +16009,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -16043,13 +16043,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>22604.95</v>
+        <v>3552.53</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2080-53163-CM25</t>
+          <t>1402-845-CM25</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16074,12 +16074,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -16108,13 +16108,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>9453.32</v>
+        <v>1826.21</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1529-418-CM25</t>
+          <t>1402-846-CM25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16139,12 +16139,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -16173,13 +16173,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>48524.66</v>
+        <v>4296.96</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1624-319-CM25</t>
+          <t>1529-418-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16204,12 +16204,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16238,13 +16238,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>7286.58</v>
+        <v>48524.66</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1402-845-CM25</t>
+          <t>1624-319-CM25</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16303,13 +16303,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1826.21</v>
+        <v>7286.58</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1402-846-CM25</t>
+          <t>2080-53163-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16334,12 +16334,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>4296.96</v>
+        <v>9453.32</v>
       </c>
     </row>
     <row r="246">
@@ -16699,7 +16699,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1350767-123-CM25</t>
+          <t>2568-2265-CM25</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16724,12 +16724,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.981.210-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>60976.94</v>
+        <v>2230.39</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1628-368-CM25</t>
+          <t>1350767-123-CM25</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16789,12 +16789,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.981.210-7</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16823,13 +16823,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>16303.99</v>
+        <v>60976.94</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2568-2265-CM25</t>
+          <t>1628-368-CM25</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16854,12 +16854,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2230.39</v>
+        <v>16303.99</v>
       </c>
     </row>
     <row r="254">
@@ -17089,7 +17089,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>889473-2773-CM25</t>
+          <t>3810-7335-CM25</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -17148,13 +17148,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>10549.65</v>
+        <v>25408.37</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3810-7335-CM25</t>
+          <t>889473-2773-CM25</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17179,12 +17179,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -17213,7 +17213,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>25408.37</v>
+        <v>10549.65</v>
       </c>
     </row>
     <row r="259">
@@ -18584,7 +18584,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1402-14-CM26</t>
+          <t>1402-15-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18643,13 +18643,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>3643.78</v>
+        <v>1252.55</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1402-15-CM26</t>
+          <t>1402-14-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18708,13 +18708,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1252.55</v>
+        <v>3643.78</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2205-7-CM26</t>
+          <t>1402-13-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18739,12 +18739,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18773,13 +18773,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>6739.81</v>
+        <v>11465</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1402-13-CM26</t>
+          <t>2107-170-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18804,12 +18804,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18838,13 +18838,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>11465</v>
+        <v>36687.99</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2107-170-CM26</t>
+          <t>2205-7-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18869,12 +18869,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>36687.99</v>
+        <v>6739.81</v>
       </c>
     </row>
     <row r="285">
@@ -19299,7 +19299,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1529-38-CM26</t>
+          <t>1628-5-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19324,12 +19324,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19358,13 +19358,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>51393.29</v>
+        <v>12813.79</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1628-5-CM26</t>
+          <t>1529-38-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19389,12 +19389,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19423,7 +19423,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>12813.79</v>
+        <v>51393.29</v>
       </c>
     </row>
     <row r="293">
@@ -20014,7 +20014,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1624-35-CM26</t>
+          <t>2107-413-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -20039,12 +20039,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -20073,7 +20073,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>9797.950000000001</v>
+        <v>54312.66</v>
       </c>
     </row>
     <row r="303">
@@ -20144,7 +20144,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2107-413-CM26</t>
+          <t>1624-35-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -20169,12 +20169,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>54312.66</v>
+        <v>9797.950000000001</v>
       </c>
     </row>
     <row r="305">
@@ -20339,7 +20339,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1622-288-CM26</t>
+          <t>2568-60-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20364,12 +20364,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20398,13 +20398,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>26394.01</v>
+        <v>3052.53</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2568-60-CM26</t>
+          <t>1622-288-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20429,12 +20429,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -20463,7 +20463,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>3052.53</v>
+        <v>26394.01</v>
       </c>
     </row>
     <row r="309">
@@ -21184,7 +21184,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1193180-16-CM26</t>
+          <t>1529-88-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -21209,12 +21209,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>60.511.060-6</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL LIBERTADOR BERNARDO  O´HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -21243,13 +21243,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>1029.41</v>
+        <v>49453.98</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1529-88-CM26</t>
+          <t>1193180-16-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -21274,12 +21274,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>60.511.060-6</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL LIBERTADOR BERNARDO  O´HIGGINS</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -21308,7 +21308,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>49453.98</v>
+        <v>1029.41</v>
       </c>
     </row>
     <row r="322">
@@ -21509,7 +21509,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1339542-16-CM26</t>
+          <t>1626-58-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21529,17 +21529,17 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -21568,13 +21568,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>5090.37</v>
+        <v>6605.93</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1626-58-CM26</t>
+          <t>1339542-16-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21594,17 +21594,17 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -21633,7 +21633,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>6605.93</v>
+        <v>5090.37</v>
       </c>
     </row>
     <row r="327">
@@ -21769,7 +21769,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1621-109-CM26</t>
+          <t>2568-91-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21794,12 +21794,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21828,13 +21828,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>11702.37</v>
+        <v>2974.83</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5336-9-CM26</t>
+          <t>1621-109-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21859,12 +21859,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>65.705.920-k</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21893,13 +21893,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1062.44</v>
+        <v>11702.37</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2568-91-CM26</t>
+          <t>5336-9-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21924,12 +21924,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.705.920-k</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21958,7 +21958,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>2974.83</v>
+        <v>1062.44</v>
       </c>
     </row>
     <row r="332">
@@ -22224,7 +22224,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1620-91-CM26</t>
+          <t>1622-546-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22249,12 +22249,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -22283,13 +22283,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>17871.87</v>
+        <v>25696.32</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1622-546-CM26</t>
+          <t>1620-91-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22348,7 +22348,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>25696.32</v>
+        <v>17871.87</v>
       </c>
     </row>
     <row r="338">
@@ -22614,7 +22614,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>594965-60-CM26</t>
+          <t>1626-80-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22639,12 +22639,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22673,13 +22673,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1636.91</v>
+        <v>6188.99</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1626-80-CM26</t>
+          <t>594965-60-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22704,12 +22704,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22738,7 +22738,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>6188.99</v>
+        <v>1636.91</v>
       </c>
     </row>
     <row r="344">
@@ -22939,7 +22939,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2207-378-CM26</t>
+          <t>1623-201-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22959,17 +22959,17 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22998,13 +22998,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>12641.88</v>
+        <v>335.48</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1623-201-CM26</t>
+          <t>2207-378-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -23024,17 +23024,17 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>335.48</v>
+        <v>12641.88</v>
       </c>
     </row>
     <row r="349">
@@ -23329,12 +23329,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1628-185-CM26</t>
+          <t>1627-760-SE26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -23354,12 +23354,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -23388,18 +23388,18 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>14528.55</v>
+        <v>80538.08</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1627-760-SE26</t>
+          <t>2107-958-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -23419,12 +23419,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -23453,13 +23453,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>80538.08</v>
+        <v>46938.39</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2107-958-CM26</t>
+          <t>1628-185-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>46938.39</v>
+        <v>14528.55</v>
       </c>
     </row>
     <row r="356">
@@ -23654,7 +23654,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1622-719-CM26</t>
+          <t>2080-5028-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23674,17 +23674,17 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23713,13 +23713,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>24701.34</v>
+        <v>12092.38</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2080-5028-CM26</t>
+          <t>1622-719-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23739,17 +23739,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23778,13 +23778,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>12092.38</v>
+        <v>24701.34</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1626-110-CM26</t>
+          <t>2107-1024-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23809,12 +23809,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23843,13 +23843,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>6248.43</v>
+        <v>47037.22</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2107-1024-CM26</t>
+          <t>1626-110-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23874,12 +23874,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23908,7 +23908,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>47037.22</v>
+        <v>6248.43</v>
       </c>
     </row>
     <row r="362">
@@ -24174,7 +24174,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>3374-73-CM26</t>
+          <t>3374-76-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24233,7 +24233,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>3273.71</v>
+        <v>6547.43</v>
       </c>
     </row>
     <row r="367">
@@ -24304,7 +24304,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>3374-76-CM26</t>
+          <t>3374-73-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>6547.43</v>
+        <v>3273.71</v>
       </c>
     </row>
     <row r="369">
@@ -24759,7 +24759,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1628-208-CM26</t>
+          <t>889473-1013-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24784,12 +24784,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -24818,13 +24818,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>16279.22</v>
+        <v>11231.36</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>889473-1013-CM26</t>
+          <t>1628-208-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -24849,12 +24849,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -24883,18 +24883,18 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>11231.36</v>
+        <v>16279.22</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1627-886-SE26</t>
+          <t>1622-838-CM26</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -24914,12 +24914,12 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -24948,18 +24948,18 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>80771.59</v>
+        <v>23992.06</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1622-838-CM26</t>
+          <t>1627-886-SE26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -24979,12 +24979,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -25013,7 +25013,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>23992.06</v>
+        <v>80771.59</v>
       </c>
     </row>
     <row r="379">
@@ -25214,7 +25214,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>522-130-CM26</t>
+          <t>1626-130-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -25239,12 +25239,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>61.602.152-4</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Hospital de Litueche</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -25273,13 +25273,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>17252.49</v>
+        <v>6357.98</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1626-130-CM26</t>
+          <t>522-130-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25304,12 +25304,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.152-4</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -25338,13 +25338,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>6357.98</v>
+        <v>17252.49</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>897-35-CM26</t>
+          <t>2207-516-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25369,12 +25369,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25403,13 +25403,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>16767.64</v>
+        <v>18694.89</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2207-516-CM26</t>
+          <t>897-35-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25434,12 +25434,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -25468,7 +25468,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>18694.89</v>
+        <v>16767.64</v>
       </c>
     </row>
     <row r="386">
@@ -25994,7 +25994,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1624-176-CM26</t>
+          <t>1529-211-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -26019,12 +26019,12 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -26034,12 +26034,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
@@ -26053,13 +26053,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>9716.67</v>
+        <v>52017.84</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1529-211-CM26</t>
+          <t>1624-176-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -26084,12 +26084,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -26118,13 +26118,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>52017.84</v>
+        <v>9716.67</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1622-998-CM26</t>
+          <t>889473-1275-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -26149,12 +26149,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -26183,13 +26183,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>23515.08</v>
+        <v>11011.21</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1079563-312-CM26</t>
+          <t>1622-998-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -26214,12 +26214,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -26229,12 +26229,12 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -26248,13 +26248,13 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>213.77</v>
+        <v>23515.08</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>889473-1275-CM26</t>
+          <t>1079563-312-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26279,12 +26279,12 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -26294,12 +26294,12 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>11011.21</v>
+        <v>213.77</v>
       </c>
     </row>
     <row r="399">
@@ -26904,12 +26904,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2776-543-CM26</t>
+          <t>1627-1161-SE26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -26924,17 +26924,17 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26963,18 +26963,18 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>13119.92</v>
+        <v>84659.45</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1627-1161-SE26</t>
+          <t>889473-1465-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -26989,17 +26989,17 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -27028,13 +27028,13 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>84659.45</v>
+        <v>11263.19</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1622-1104-CM26</t>
+          <t>2776-543-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -27059,12 +27059,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -27093,13 +27093,13 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>25146.51</v>
+        <v>13119.92</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>889473-1465-CM26</t>
+          <t>2107-1711-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -27124,12 +27124,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -27139,12 +27139,12 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
@@ -27158,13 +27158,13 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>11263.19</v>
+        <v>56852.97</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2107-1711-CM26</t>
+          <t>1622-1104-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -27189,12 +27189,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -27204,12 +27204,12 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -27223,13 +27223,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>56852.97</v>
+        <v>25146.51</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1624-196-CM26</t>
+          <t>2080-8552-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27254,12 +27254,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -27288,13 +27288,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>9916.34</v>
+        <v>12617.69</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1628-247-CM26</t>
+          <t>2205-123-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27319,12 +27319,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -27353,13 +27353,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>16457.65</v>
+        <v>6397.64</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2080-8552-CM26</t>
+          <t>1628-247-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27384,12 +27384,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -27418,13 +27418,13 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>12617.69</v>
+        <v>16457.65</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2205-123-CM26</t>
+          <t>1624-196-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -27449,12 +27449,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -27483,7 +27483,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>6397.64</v>
+        <v>9916.34</v>
       </c>
     </row>
     <row r="417">
@@ -27684,7 +27684,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>522-176-CM26</t>
+          <t>594965-148-CM26</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27709,12 +27709,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>61.602.152-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Hospital de Litueche</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -27743,13 +27743,13 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>19213.18</v>
+        <v>531.5599999999999</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>594965-148-CM26</t>
+          <t>1626-181-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27774,12 +27774,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -27808,13 +27808,13 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>531.5599999999999</v>
+        <v>6399.94</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>1626-181-CM26</t>
+          <t>522-176-CM26</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -27839,12 +27839,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.152-4</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -27873,7 +27873,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>6399.94</v>
+        <v>19213.18</v>
       </c>
     </row>
     <row r="423">
@@ -28484,7 +28484,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -28659,7 +28659,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>3374-126-CM26</t>
+          <t>2107-2009-CM26</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -28684,12 +28684,12 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -28699,12 +28699,12 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
@@ -28718,7 +28718,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>184.49</v>
+        <v>53936.31</v>
       </c>
     </row>
     <row r="436">
@@ -28744,7 +28744,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -28789,7 +28789,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2107-2009-CM26</t>
+          <t>3374-126-CM26</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -28809,17 +28809,17 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -28829,12 +28829,12 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
@@ -28848,13 +28848,13 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>53936.31</v>
+        <v>184.49</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>1628-294-CM26</t>
+          <t>889473-1764-CM26</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -28874,17 +28874,17 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -28913,7 +28913,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>15468.7</v>
+        <v>7130.95</v>
       </c>
     </row>
     <row r="439">
@@ -28984,7 +28984,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>889473-1764-CM26</t>
+          <t>1628-294-CM26</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -29004,17 +29004,17 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -29043,18 +29043,18 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>7130.95</v>
+        <v>15468.7</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>1529-249-CM26</t>
+          <t>1627-1299-SE26</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -29069,17 +29069,17 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -29089,12 +29089,12 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
@@ -29108,18 +29108,18 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>50076.5</v>
+        <v>82847.95</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>1627-1299-SE26</t>
+          <t>1529-249-CM26</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -29134,46 +29134,631 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>61.602.140-0</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M442" s="2" t="n">
+        <v>50076.5</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>1626-206-CM26</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>61.602.150-8</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Hospital de Lolol</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M443" s="2" t="n">
+        <v>5694.54</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>1626-189-CM26</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>61.602.150-8</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Hospital de Lolol</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M444" s="2" t="n">
+        <v>1860.54</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>1623-459-CM26</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>61.602.142-7</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M445" s="2" t="n">
+        <v>12399.59</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>1621-294-CM26</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>61.602.151-6</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M446" s="2" t="n">
+        <v>10996.57</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>3374-142-CM26</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>61.101.006-0</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M447" s="2" t="n">
+        <v>8156.69</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>1350767-168-CM26</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>61.981.210-7</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M448" s="2" t="n">
+        <v>361.44</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>3283-60-CM26</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M449" s="2" t="n">
+        <v>9346.51</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2205-194-CM26</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>61.602.145-1</t>
-        </is>
-      </c>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
-        </is>
-      </c>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="I442" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J442" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K442" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L442" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M442" s="2" t="n">
-        <v>82847.95</v>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>61.602.143-5</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M450" s="2" t="n">
+        <v>6912.16</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>1622-1347-CM26</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>61.602.141-9</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M451" s="2" t="n">
+        <v>24326.46</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/o-higgins.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/o-higgins.xlsx
@@ -29784,7 +29784,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -29849,7 +29849,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
